--- a/nonprofit_employee_forms/007_volunteer_hours_log_form--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/007_volunteer_hours_log_form--nonprofit_employee_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>volunteer_hours_log_form</t>
+          <t>volunteer_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Volunteer Hours Log</t>
+          <t>Volunteer Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,19 +533,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>volunteer_name</t>
+          <t>event_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Volunteer Name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Enter volunteer name</t>
-        </is>
-      </c>
+          <t>Event Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -555,24 +551,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>hours_info</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Date of event</t>
-        </is>
-      </c>
+          <t>Hours Worked</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -587,19 +579,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked</t>
+          <t>event_info_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hours Worked</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Number of hours worked</t>
-        </is>
-      </c>
+          <t>Additional Event Information</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -614,19 +602,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>volunteer_name_2</t>
+          <t>additional_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Volunteer Name</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Enter volunteer name</t>
-        </is>
-      </c>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -636,24 +620,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_date_2</t>
+          <t>hours_info_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Date of event</t>
-        </is>
-      </c>
+          <t>Hours Worked Summary</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -668,19 +648,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hours_worked_2</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hours Worked</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Number of hours worked</t>
-        </is>
-      </c>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -695,19 +671,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>volunteer_name_3</t>
+          <t>hours_info_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Volunteer Name</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter volunteer name</t>
-        </is>
-      </c>
+          <t>Total Hours Worked</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -717,133 +689,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>event_date_3</t>
+          <t>hours_info_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Date of event</t>
-        </is>
-      </c>
+          <t>Hours Worked Summary 2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>hours_worked_3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Hours Worked</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Number of hours worked</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>event_description</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Event Description</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Event description</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>event_location</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Event Location</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Event location</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>volunteer_supervisor</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Volunteer Supervisor</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Enter volunteer supervisor</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
